--- a/data/l1_project/hero_battery_factory_project.xlsx
+++ b/data/l1_project/hero_battery_factory_project.xlsx
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[합성] 셀 설비 1차 선적 서보 모터 자석 부품(중국 공장 직송)</t>
+          <t>[합성] 셀 설비 1차 선적 서보 모터 자석 부품(희토류 자석 포함, 중국 공장 직송)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>중국 희토류 수출 허가(선적마다), 원산지 증명</t>
+          <t>원산지 증명</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>중국 희토류 수출 허가(선적마다)</t>
+          <t>원산지 증명</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>중국 희토류 수출 허가(선적마다), 교정 성적서</t>
+          <t>원산지 증명, 교정 성적서</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
